--- a/data/trans_orig/P36B11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B11-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de pescado en 2007</t>
+          <t>Población según la frecuencia de consumo de pescado en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25969</t>
+          <t>25201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,82 +747,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>15292</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8631</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24318</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>31221</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>21351</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>42925</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15292</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8976</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24183</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>31221</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>21766</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66391</t>
+          <t>65617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102834</t>
+          <t>100261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66048</t>
+          <t>65332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100900</t>
+          <t>98796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140702</t>
+          <t>141818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>191864</t>
+          <t>190176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>447162</t>
+          <t>446837</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>509906</t>
+          <t>510889</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>648760</t>
+          <t>649870</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>721503</t>
+          <t>723016</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1115108</t>
+          <t>1114553</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1212960</t>
+          <t>1211526</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>386868</t>
+          <t>388192</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>450553</t>
+          <t>450652</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>462611</t>
+          <t>464004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>532103</t>
+          <t>531829</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>871270</t>
+          <t>874685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>965748</t>
+          <t>967462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46134</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>26139</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48790</t>
+          <t>49535</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53631</t>
+          <t>54683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86103</t>
+          <t>87583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42839</t>
+          <t>42607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23977</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46480</t>
+          <t>46039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49233</t>
+          <t>48535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81514</t>
+          <t>81717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123960</t>
+          <t>124158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171546</t>
+          <t>170242</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109852</t>
+          <t>109467</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153249</t>
+          <t>153883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245832</t>
+          <t>244963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306383</t>
+          <t>306254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>838193</t>
+          <t>840499</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>921674</t>
+          <t>921372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>827041</t>
+          <t>829910</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>905628</t>
+          <t>908182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1691261</t>
+          <t>1687055</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1803911</t>
+          <t>1809368</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>570069</t>
+          <t>565754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>647480</t>
+          <t>645648</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>477036</t>
+          <t>473133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>553927</t>
+          <t>550090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1067032</t>
+          <t>1070879</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1182365</t>
+          <t>1180330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45101</t>
+          <t>44341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29302</t>
+          <t>29031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54749</t>
+          <t>54342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55074</t>
+          <t>56262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89586</t>
+          <t>91639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29955</t>
+          <t>27004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44857</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73562</t>
+          <t>73493</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24486</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47820</t>
+          <t>47945</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73784</t>
+          <t>76160</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111297</t>
+          <t>114276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>246649</t>
+          <t>242862</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>295967</t>
+          <t>295322</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>256506</t>
+          <t>255817</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>299843</t>
+          <t>303052</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>514753</t>
+          <t>515659</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>578584</t>
+          <t>579872</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>181884</t>
+          <t>182361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>231487</t>
+          <t>231668</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125423</t>
+          <t>125525</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165880</t>
+          <t>165863</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>322794</t>
+          <t>321718</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>385718</t>
+          <t>382455</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>27947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69327</t>
+          <t>67104</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77277</t>
+          <t>79659</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93462</t>
+          <t>91118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133681</t>
+          <t>134218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258332</t>
+          <t>255562</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>318732</t>
+          <t>318675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>215991</t>
+          <t>217406</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>275959</t>
+          <t>279537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>491676</t>
+          <t>489144</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>582750</t>
+          <t>578795</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1571743</t>
+          <t>1571575</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1686602</t>
+          <t>1685085</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1775576</t>
+          <t>1772339</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1893556</t>
+          <t>1884836</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3375403</t>
+          <t>3366839</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3544675</t>
+          <t>3535574</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1181914</t>
+          <t>1173335</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1290554</t>
+          <t>1285845</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1102121</t>
+          <t>1104911</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1208195</t>
+          <t>1212232</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2316651</t>
+          <t>2313757</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2470487</t>
+          <t>2469958</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59659</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>94283</t>
+          <t>93269</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68410</t>
+          <t>67886</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105279</t>
+          <t>104954</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136328</t>
+          <t>135858</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>185700</t>
+          <t>186991</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de pescado en 2012</t>
+          <t>Población según la frecuencia de consumo de pescado en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>23673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>16873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38520</t>
+          <t>38480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89538</t>
+          <t>89771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132735</t>
+          <t>130159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>83710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122408</t>
+          <t>122410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179611</t>
+          <t>181627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238132</t>
+          <t>239567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>491221</t>
+          <t>489655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>552989</t>
+          <t>553493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>681945</t>
+          <t>685198</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754394</t>
+          <t>756100</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1196797</t>
+          <t>1195275</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1295212</t>
+          <t>1295328</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>274600</t>
+          <t>274902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>332179</t>
+          <t>331174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>431357</t>
+          <t>427696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>501032</t>
+          <t>498594</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>722685</t>
+          <t>718838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>811578</t>
+          <t>813982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33889</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24595</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47495</t>
+          <t>48251</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44851</t>
+          <t>45119</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76662</t>
+          <t>77741</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>20243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42637</t>
+          <t>43455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>18461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39523</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43461</t>
+          <t>43450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73022</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168708</t>
+          <t>167620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222072</t>
+          <t>224930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107135</t>
+          <t>108454</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152974</t>
+          <t>151609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>286630</t>
+          <t>285956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>357795</t>
+          <t>355710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>957357</t>
+          <t>955221</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1050817</t>
+          <t>1052175</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>861690</t>
+          <t>862068</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>952032</t>
+          <t>952495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1850944</t>
+          <t>1845468</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1975178</t>
+          <t>1970379</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>625797</t>
+          <t>627861</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>713335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>602404</t>
+          <t>605089</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>692577</t>
+          <t>689275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1254327</t>
+          <t>1258658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1373837</t>
+          <t>1376418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48484</t>
+          <t>49538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81754</t>
+          <t>85288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34309</t>
+          <t>33310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61785</t>
+          <t>60170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90662</t>
+          <t>90983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134041</t>
+          <t>134217</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23068</t>
+          <t>23650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17219</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37719</t>
+          <t>37251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21047</t>
+          <t>21121</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41958</t>
+          <t>42319</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42899</t>
+          <t>43379</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72935</t>
+          <t>71216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>227216</t>
+          <t>226914</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>273522</t>
+          <t>273549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202591</t>
+          <t>202471</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>247411</t>
+          <t>249385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>442206</t>
+          <t>441014</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>507425</t>
+          <t>507939</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>169169</t>
+          <t>169069</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>216032</t>
+          <t>213533</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>156271</t>
+          <t>154962</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>200598</t>
+          <t>199770</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>335303</t>
+          <t>336622</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>399342</t>
+          <t>402258</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30907</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38210</t>
+          <t>39006</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34413</t>
+          <t>34027</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66785</t>
+          <t>64307</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33597</t>
+          <t>33735</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63187</t>
+          <t>60433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77789</t>
+          <t>77214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117438</t>
+          <t>114277</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>292794</t>
+          <t>293212</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>366181</t>
+          <t>364749</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>228818</t>
+          <t>228999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>294637</t>
+          <t>288131</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>542210</t>
+          <t>537847</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638852</t>
+          <t>637258</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1714430</t>
+          <t>1711233</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1833275</t>
+          <t>1839252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1787678</t>
+          <t>1789483</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1910347</t>
+          <t>1910050</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3550358</t>
+          <t>3541312</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3718858</t>
+          <t>3712985</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1117387</t>
+          <t>1114064</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1227421</t>
+          <t>1229120</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1226032</t>
+          <t>1228359</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1345807</t>
+          <t>1347243</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2370431</t>
+          <t>2374849</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2528697</t>
+          <t>2534298</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74622</t>
+          <t>75668</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115185</t>
+          <t>115115</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81434</t>
+          <t>81206</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>122484</t>
+          <t>122392</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>169044</t>
+          <t>168886</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>225968</t>
+          <t>225144</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de pescado en 2016</t>
+          <t>Población según la frecuencia de consumo de pescado en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>20995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>23783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38383</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51988</t>
+          <t>51971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83218</t>
+          <t>82973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50115</t>
+          <t>49710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82308</t>
+          <t>79935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107893</t>
+          <t>109333</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151379</t>
+          <t>154667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>421974</t>
+          <t>418812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>475834</t>
+          <t>473547</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>559122</t>
+          <t>562913</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>622910</t>
+          <t>625896</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1001619</t>
+          <t>1003973</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1083477</t>
+          <t>1087058</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>186503</t>
+          <t>185619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>235751</t>
+          <t>236575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>266323</t>
+          <t>264667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>326135</t>
+          <t>321781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>471093</t>
+          <t>469160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>545036</t>
+          <t>543838</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>35694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>26497</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52040</t>
+          <t>51866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>23498</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47922</t>
+          <t>46791</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18573</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39129</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46827</t>
+          <t>45351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79274</t>
+          <t>78214</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>187416</t>
+          <t>188601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244559</t>
+          <t>243944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171895</t>
+          <t>173948</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>227395</t>
+          <t>227815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374679</t>
+          <t>374327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>452577</t>
+          <t>453848</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1212461</t>
+          <t>1208685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1304075</t>
+          <t>1298359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1141130</t>
+          <t>1146732</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1232075</t>
+          <t>1238341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2379009</t>
+          <t>2385605</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2507696</t>
+          <t>2516334</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,05%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>504065</t>
+          <t>507629</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>587120</t>
+          <t>588104</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>502814</t>
+          <t>497432</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>579747</t>
+          <t>576417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1024486</t>
+          <t>1022533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1137346</t>
+          <t>1136884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>32931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21391</t>
+          <t>20745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43443</t>
+          <t>43117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38100</t>
+          <t>37939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68937</t>
+          <t>69819</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14561</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28427</t>
+          <t>28991</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32480</t>
+          <t>31548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59555</t>
+          <t>59767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31140</t>
+          <t>31520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58544</t>
+          <t>57352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73287</t>
+          <t>72482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110307</t>
+          <t>112370</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>317713</t>
+          <t>318006</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>364885</t>
+          <t>365812</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>304670</t>
+          <t>301231</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>349024</t>
+          <t>347617</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>633036</t>
+          <t>635025</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>699992</t>
+          <t>698850</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126211</t>
+          <t>126439</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>167519</t>
+          <t>170387</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>137946</t>
+          <t>138409</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>181293</t>
+          <t>181892</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>277653</t>
+          <t>276994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>339184</t>
+          <t>336848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39478</t>
+          <t>40353</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69970</t>
+          <t>71168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,47 +8711,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>53376</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>41096</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>71383</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>53376</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>41552</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>70013</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87786</t>
+          <t>86335</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126652</t>
+          <t>128669</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>294609</t>
+          <t>294422</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>360480</t>
+          <t>365152</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>272179</t>
+          <t>274036</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>337858</t>
+          <t>340706</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>584739</t>
+          <t>583572</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>682431</t>
+          <t>686558</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1992941</t>
+          <t>1985812</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2110977</t>
+          <t>2102824</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2051007</t>
+          <t>2049242</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2166453</t>
+          <t>2168824</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4081925</t>
+          <t>4070220</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4242863</t>
+          <t>4242472</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>845950</t>
+          <t>848725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>952164</t>
+          <t>958812</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>935878</t>
+          <t>935276</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1045955</t>
+          <t>1044914</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1819418</t>
+          <t>1813629</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1969162</t>
+          <t>1971644</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29104</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54725</t>
+          <t>55558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47309</t>
+          <t>49760</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79736</t>
+          <t>80245</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>83587</t>
+          <t>84589</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>124833</t>
+          <t>126319</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B11-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25201</t>
+          <t>26475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24318</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21351</t>
+          <t>21329</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42925</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65617</t>
+          <t>67820</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100261</t>
+          <t>101771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65332</t>
+          <t>65919</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98796</t>
+          <t>100434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141818</t>
+          <t>140992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>190176</t>
+          <t>192107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>446837</t>
+          <t>447011</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>510889</t>
+          <t>509585</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>649870</t>
+          <t>641194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>723016</t>
+          <t>714948</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1114553</t>
+          <t>1113881</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1211526</t>
+          <t>1212387</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>388192</t>
+          <t>388909</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>450652</t>
+          <t>451783</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>464004</t>
+          <t>463722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>531829</t>
+          <t>535443</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>874685</t>
+          <t>875201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>967462</t>
+          <t>968776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>24150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>46479</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26139</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49535</t>
+          <t>49382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>54504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87583</t>
+          <t>85996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42607</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22817</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46039</t>
+          <t>46588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48535</t>
+          <t>49142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81717</t>
+          <t>79880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124158</t>
+          <t>124448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170242</t>
+          <t>167991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109467</t>
+          <t>109909</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153883</t>
+          <t>154038</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244963</t>
+          <t>244173</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306254</t>
+          <t>308336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>840499</t>
+          <t>833292</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>921372</t>
+          <t>915781</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>829910</t>
+          <t>829663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>908182</t>
+          <t>907089</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1687055</t>
+          <t>1686189</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1809368</t>
+          <t>1805944</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>565754</t>
+          <t>571429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>645648</t>
+          <t>649154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>473133</t>
+          <t>477550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>550090</t>
+          <t>550559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1070879</t>
+          <t>1066000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1180330</t>
+          <t>1179566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21703</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44341</t>
+          <t>45222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29031</t>
+          <t>29356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54342</t>
+          <t>53443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56262</t>
+          <t>55945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91639</t>
+          <t>91279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20494</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27004</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73493</t>
+          <t>72821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>23794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47945</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76160</t>
+          <t>74171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114276</t>
+          <t>110945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242862</t>
+          <t>243473</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>295322</t>
+          <t>294157</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>255817</t>
+          <t>255972</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>303052</t>
+          <t>299341</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>515659</t>
+          <t>515475</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>579872</t>
+          <t>579525</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>182361</t>
+          <t>185946</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>231668</t>
+          <t>232960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125525</t>
+          <t>124083</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165863</t>
+          <t>164186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>321718</t>
+          <t>320813</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>382455</t>
+          <t>382930</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27947</t>
+          <t>28989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67104</t>
+          <t>67937</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,82 +2793,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>60318</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>45413</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>77473</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>112229</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>93964</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>136185</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>2,05%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>60318</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>46826</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>79659</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>112229</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>91118</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>134218</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255562</t>
+          <t>255894</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>318675</t>
+          <t>319490</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217406</t>
+          <t>214090</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>279537</t>
+          <t>274879</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>489144</t>
+          <t>489226</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>578795</t>
+          <t>578789</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1571575</t>
+          <t>1571522</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1685085</t>
+          <t>1687908</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1772339</t>
+          <t>1769230</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1884836</t>
+          <t>1885215</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3366839</t>
+          <t>3378998</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3535574</t>
+          <t>3539825</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1173335</t>
+          <t>1182232</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1285845</t>
+          <t>1288637</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1104911</t>
+          <t>1102980</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1212232</t>
+          <t>1213222</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2313757</t>
+          <t>2313020</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2469958</t>
+          <t>2469425</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58785</t>
+          <t>60618</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93269</t>
+          <t>95392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67886</t>
+          <t>65092</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>104954</t>
+          <t>102185</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>135858</t>
+          <t>135977</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>186991</t>
+          <t>186452</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23673</t>
+          <t>20816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16873</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89771</t>
+          <t>87539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130159</t>
+          <t>128518</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83710</t>
+          <t>83402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122410</t>
+          <t>121839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>181627</t>
+          <t>182125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239567</t>
+          <t>239569</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>489655</t>
+          <t>490541</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>553493</t>
+          <t>556612</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>685198</t>
+          <t>680298</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>756100</t>
+          <t>754566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1195275</t>
+          <t>1193717</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1295328</t>
+          <t>1289892</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>55,98%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>274902</t>
+          <t>270350</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>331174</t>
+          <t>330657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>427696</t>
+          <t>432420</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>498594</t>
+          <t>499019</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>718838</t>
+          <t>720751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>813982</t>
+          <t>815399</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>35039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24595</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48251</t>
+          <t>50502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>45119</t>
+          <t>45636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77741</t>
+          <t>77962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43455</t>
+          <t>43790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40784</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43450</t>
+          <t>43015</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75884</t>
+          <t>75753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167620</t>
+          <t>166649</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>224930</t>
+          <t>221873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108454</t>
+          <t>107013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151609</t>
+          <t>151753</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285956</t>
+          <t>286133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>355710</t>
+          <t>355481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>955221</t>
+          <t>958548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1052175</t>
+          <t>1047624</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>862068</t>
+          <t>861979</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>952495</t>
+          <t>951052</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1845468</t>
+          <t>1846498</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1970379</t>
+          <t>1973703</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>627861</t>
+          <t>633363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>713335</t>
+          <t>717701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>605089</t>
+          <t>600829</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>689275</t>
+          <t>687727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1258658</t>
+          <t>1254274</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1376418</t>
+          <t>1378528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49538</t>
+          <t>47535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85288</t>
+          <t>82017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33310</t>
+          <t>33237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60170</t>
+          <t>63581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90983</t>
+          <t>90049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134217</t>
+          <t>133005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>17022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23650</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16748</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37251</t>
+          <t>37912</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21121</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42319</t>
+          <t>43741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43379</t>
+          <t>43732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71216</t>
+          <t>72393</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>226914</t>
+          <t>227722</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>273549</t>
+          <t>275100</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202471</t>
+          <t>203174</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>249385</t>
+          <t>247867</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>441014</t>
+          <t>444630</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>507939</t>
+          <t>508645</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>169069</t>
+          <t>167768</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>213533</t>
+          <t>214191</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>154962</t>
+          <t>157879</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>199770</t>
+          <t>203035</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>336622</t>
+          <t>337483</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>402258</t>
+          <t>400830</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>30847</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>37805</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34027</t>
+          <t>35146</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64307</t>
+          <t>65038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33735</t>
+          <t>34369</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60433</t>
+          <t>61993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77214</t>
+          <t>73945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114277</t>
+          <t>116193</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>293212</t>
+          <t>291347</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>364749</t>
+          <t>364780</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>228999</t>
+          <t>231402</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>288131</t>
+          <t>292724</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>537847</t>
+          <t>539491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>637258</t>
+          <t>635055</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1711233</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1839252</t>
+          <t>1834109</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1789483</t>
+          <t>1790529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1910050</t>
+          <t>1911044</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3541312</t>
+          <t>3544631</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3712985</t>
+          <t>3726885</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1114064</t>
+          <t>1110089</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1229120</t>
+          <t>1224888</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1228359</t>
+          <t>1225291</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1347243</t>
+          <t>1343903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2374849</t>
+          <t>2365898</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2534298</t>
+          <t>2536369</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75668</t>
+          <t>75636</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115115</t>
+          <t>116537</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81206</t>
+          <t>82623</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>122392</t>
+          <t>125246</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>168886</t>
+          <t>168915</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>225144</t>
+          <t>224523</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>39358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51971</t>
+          <t>53280</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82973</t>
+          <t>84149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49710</t>
+          <t>50124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79935</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109333</t>
+          <t>108820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154667</t>
+          <t>152474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>418812</t>
+          <t>424607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>473547</t>
+          <t>472914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>562913</t>
+          <t>561977</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>625896</t>
+          <t>626362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1003973</t>
+          <t>1001281</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1087058</t>
+          <t>1083435</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,13%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>185619</t>
+          <t>187965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>236575</t>
+          <t>233215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>264667</t>
+          <t>266631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>321781</t>
+          <t>327737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>469160</t>
+          <t>468269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>543838</t>
+          <t>543002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35694</t>
+          <t>36650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26497</t>
+          <t>27233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51866</t>
+          <t>51600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23498</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46791</t>
+          <t>47055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>19303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>39696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,47 +7382,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>60950</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>46733</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>78029</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,92%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>60950</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>45351</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>78214</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188601</t>
+          <t>186393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243944</t>
+          <t>242903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173948</t>
+          <t>173595</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>227815</t>
+          <t>227699</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374327</t>
+          <t>374519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>453848</t>
+          <t>449919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1208685</t>
+          <t>1210526</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1298359</t>
+          <t>1301531</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1146732</t>
+          <t>1147869</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1238341</t>
+          <t>1236942</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2385605</t>
+          <t>2386217</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2516334</t>
+          <t>2509744</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>507629</t>
+          <t>506702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>588104</t>
+          <t>584078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>497432</t>
+          <t>494602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>576417</t>
+          <t>576294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1022533</t>
+          <t>1027776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1136884</t>
+          <t>1140989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32931</t>
+          <t>33344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43117</t>
+          <t>43189</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37939</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69819</t>
+          <t>71489</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28991</t>
+          <t>29291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31548</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59767</t>
+          <t>60144</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31520</t>
+          <t>32256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57352</t>
+          <t>57578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72482</t>
+          <t>71842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112370</t>
+          <t>110104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>318006</t>
+          <t>316536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>365812</t>
+          <t>365467</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>301231</t>
+          <t>304393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>347617</t>
+          <t>352626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>635025</t>
+          <t>634864</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>698850</t>
+          <t>702993</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,2%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126439</t>
+          <t>125191</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>170387</t>
+          <t>170329</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>138409</t>
+          <t>136701</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>181892</t>
+          <t>180322</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>276994</t>
+          <t>273926</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>336848</t>
+          <t>335104</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>13198</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>21422</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>39851</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71168</t>
+          <t>67897</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41096</t>
+          <t>39667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71383</t>
+          <t>69343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86335</t>
+          <t>87247</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128669</t>
+          <t>128235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>294422</t>
+          <t>295344</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>365152</t>
+          <t>365110</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>274036</t>
+          <t>275521</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>340706</t>
+          <t>342942</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>583572</t>
+          <t>584747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>686558</t>
+          <t>684634</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1985812</t>
+          <t>1990069</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2102824</t>
+          <t>2104944</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2049242</t>
+          <t>2056023</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2168824</t>
+          <t>2170538</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4070220</t>
+          <t>4068144</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4242472</t>
+          <t>4235631</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,44%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>848725</t>
+          <t>848746</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>958812</t>
+          <t>952240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>935276</t>
+          <t>934242</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1044914</t>
+          <t>1044718</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1813629</t>
+          <t>1824161</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1971644</t>
+          <t>1973124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>27163</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55558</t>
+          <t>54616</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49760</t>
+          <t>48707</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>80245</t>
+          <t>81032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>84589</t>
+          <t>83444</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>126319</t>
+          <t>124598</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
